--- a/data/export/2026-10-04-operations.xlsx
+++ b/data/export/2026-10-04-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,7 +2394,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2363,22 +2407,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2510,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2523,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>07:01</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2571,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2590,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2626,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2687,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2706,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2742,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2803,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2822,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2858,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2919,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2938,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2974,2939 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-operations.xlsx
+++ b/data/export/2026-10-04-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,14 +1215,14 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -1222,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1922,7 +1970,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2075,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2042,7 +2090,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2195,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2162,7 +2210,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,41 +2436,45 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2455,12 +2507,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2474,7 +2526,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2499,46 +2551,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2571,12 +2627,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2590,7 +2646,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2615,46 +2671,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2687,12 +2747,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2706,7 +2766,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2731,46 +2791,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2803,12 +2867,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2822,7 +2886,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2847,46 +2911,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2919,12 +2987,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2938,7 +3006,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2963,46 +3031,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3035,12 +3107,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3054,7 +3126,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3079,46 +3151,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3151,12 +3227,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3170,7 +3246,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3195,46 +3271,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3267,12 +3347,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3286,7 +3366,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3311,18 +3391,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3419,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3345,7 +3429,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3355,40 +3439,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3402,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3412,33 +3500,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3543,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3461,7 +3553,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3471,40 +3563,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3518,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3528,33 +3624,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3567,60 +3667,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3634,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3644,17 +3748,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3664,13 +3768,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3791,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3693,7 +3801,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3703,40 +3811,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3750,7 +3862,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3760,17 +3872,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3780,13 +3892,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3915,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3809,7 +3925,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3819,40 +3935,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3866,7 +3986,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3876,33 +3996,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3915,7 +4039,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3925,7 +4049,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3963,12 +4087,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3982,7 +4106,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4018,7 +4142,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4155,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4041,7 +4165,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4079,12 +4203,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4098,7 +4222,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4134,7 +4258,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4271,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4157,7 +4281,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4195,12 +4319,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4214,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4250,7 +4374,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4387,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4273,7 +4397,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4311,12 +4435,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4330,7 +4454,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4366,7 +4490,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4503,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4389,7 +4513,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4427,12 +4551,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4446,7 +4570,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4482,7 +4606,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4495,22 +4619,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4543,12 +4667,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4562,7 +4686,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4598,77 +4722,73 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4682,7 +4802,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4692,107 +4812,99 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4806,7 +4918,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4816,65 +4928,61 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4907,12 +5015,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4926,7 +5034,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4962,77 +5070,73 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5046,7 +5150,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5056,17 +5160,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5076,45 +5180,41 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5147,12 +5247,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5166,7 +5266,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5202,35 +5302,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5263,12 +5363,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5282,7 +5382,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5318,35 +5418,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5379,12 +5479,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5398,7 +5498,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5434,35 +5534,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5495,12 +5595,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5514,7 +5614,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5539,50 +5639,46 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5615,12 +5711,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5634,7 +5730,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5670,35 +5766,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5731,12 +5827,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5750,7 +5846,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5786,35 +5882,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5847,12 +5943,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5866,47 +5962,3131 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="X65" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA65" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
+      <c r="AB65" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC46" s="2" t="inlineStr">
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="AD46" s="2" t="inlineStr">
-        <is>
-          <t>2/9</t>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-operations.xlsx
+++ b/data/export/2026-10-04-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD72"/>
+  <dimension ref="A1:AD74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1883,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1960,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2003,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2036,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2060,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2080,7 +2088,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2276,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2315,7 +2323,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2392,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2512,7 +2520,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2566,7 +2574,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2806,7 +2814,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2880,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2992,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3112,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3232,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3276,7 +3284,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3299,22 +3307,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3347,12 +3355,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3366,7 +3374,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3391,92 +3399,84 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3500,22 +3500,22 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3543,24 +3543,24 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3573,24 +3573,24 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3667,24 +3667,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>06:18</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3697,24 +3697,24 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3763,22 +3763,22 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3887,17 +3887,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -3915,24 +3915,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3945,24 +3945,24 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4059,32 +4059,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4092,7 +4096,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4106,7 +4110,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4116,33 +4120,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4155,60 +4163,64 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:44</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4222,7 +4234,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4232,17 +4244,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4252,13 +4264,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4271,22 +4287,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4319,12 +4335,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4338,7 +4354,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4387,22 +4403,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:01</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4440,7 +4456,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4454,7 +4470,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4503,22 +4519,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4551,12 +4567,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4570,7 +4586,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4619,7 +4635,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4629,7 +4645,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4667,12 +4683,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4686,7 +4702,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4735,32 +4751,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq40，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4783,12 +4799,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4796,13 +4812,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4851,22 +4883,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4899,12 +4931,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4967,7 +4999,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4977,7 +5009,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5015,12 +5047,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5034,7 +5066,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5083,22 +5115,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5131,12 +5163,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5150,7 +5182,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5199,22 +5231,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5247,12 +5279,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5315,22 +5347,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5363,12 +5395,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5382,7 +5414,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5431,22 +5463,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5479,12 +5511,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5547,22 +5579,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5600,7 +5632,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5614,7 +5646,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5663,22 +5695,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5711,12 +5743,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5779,22 +5811,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5827,12 +5859,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5846,7 +5878,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5895,22 +5927,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5943,12 +5975,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6011,22 +6043,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6064,7 +6096,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6078,7 +6110,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6127,22 +6159,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6175,12 +6207,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6243,7 +6275,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6253,7 +6285,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6291,12 +6323,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6310,7 +6342,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6359,22 +6391,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6412,7 +6444,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6426,7 +6458,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6475,22 +6507,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6528,7 +6560,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6542,7 +6574,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6567,22 +6599,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6595,22 +6623,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6648,7 +6676,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6662,7 +6690,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6697,12 +6725,12 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -6715,22 +6743,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6763,12 +6791,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6782,7 +6810,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6807,18 +6835,22 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -6831,22 +6863,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6879,12 +6911,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6898,7 +6930,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6923,92 +6955,84 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7022,7 +7046,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7032,17 +7056,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7057,82 +7081,78 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7146,7 +7166,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7156,17 +7176,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7181,12 +7201,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7219,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7209,7 +7229,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7229,12 +7249,12 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
@@ -7256,7 +7276,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7270,7 +7290,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7305,12 +7325,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7343,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7333,7 +7353,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7353,24 +7373,24 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -7380,7 +7400,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7394,7 +7414,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7429,12 +7449,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7467,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7457,7 +7477,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7467,32 +7487,36 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7500,7 +7524,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7514,7 +7538,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7524,17 +7548,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7544,13 +7568,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7591,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7573,7 +7601,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7593,7 +7621,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7605,22 +7633,22 @@
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7634,7 +7662,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7687,7 +7715,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7697,7 +7725,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7707,40 +7735,44 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7754,7 +7786,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7764,33 +7796,37 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7839,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7813,7 +7849,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7823,32 +7859,36 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7856,7 +7896,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7870,7 +7910,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7880,17 +7920,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7905,12 +7945,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7963,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7933,7 +7973,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7971,12 +8011,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7990,7 +8030,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8039,7 +8079,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8049,7 +8089,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8087,12 +8127,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8106,7 +8146,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8131,18 +8171,22 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -8155,22 +8199,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8203,12 +8247,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8222,7 +8266,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8247,22 +8291,18 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -8275,22 +8315,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8323,12 +8363,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8342,7 +8382,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8367,22 +8407,18 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8431,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8405,7 +8441,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8443,12 +8479,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8462,7 +8498,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8487,18 +8523,22 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8551,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8521,7 +8561,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8564,7 +8604,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8578,7 +8618,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8613,12 +8653,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8671,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8641,7 +8681,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8679,12 +8719,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8698,7 +8738,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8723,7 +8763,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8747,7 +8787,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8757,7 +8797,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8795,12 +8835,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8814,7 +8854,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8839,18 +8879,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -8863,22 +8907,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8916,7 +8960,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8930,7 +8974,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8965,12 +9009,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -8983,22 +9027,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -9031,12 +9075,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9050,7 +9094,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9085,6 +9129,242 @@
       </c>
       <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
         <is>
           <t>—/12</t>
         </is>

--- a/data/export/2026-10-04-operations.xlsx
+++ b/data/export/2026-10-04-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD74"/>
+  <dimension ref="A1:AD96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1893,24 +1893,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2131,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2188,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2284,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2308,17 +2316,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2328,13 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2367,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2400,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2424,37 +2440,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2487,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2520,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2544,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2607,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2640,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2664,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2727,32 +2751,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2760,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2784,37 +2812,37 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2847,32 +2875,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2880,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2904,17 +2936,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2924,17 +2956,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3039,7 +3071,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3054,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3159,7 +3191,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3174,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3360,7 +3392,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3404,13 +3436,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3520,87 +3556,83 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3646,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3624,107 +3656,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3766,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3748,107 +3776,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3862,7 +3886,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3872,107 +3896,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3986,7 +4006,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3996,107 +4016,103 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4110,7 +4126,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4120,22 +4136,22 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4145,82 +4161,78 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4234,7 +4246,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4244,37 +4256,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4299,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4297,7 +4309,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4307,40 +4319,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4354,7 +4370,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4364,33 +4380,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4423,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4413,7 +4433,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4423,40 +4443,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4470,7 +4494,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4480,33 +4504,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4547,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4529,7 +4557,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4539,40 +4567,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4586,7 +4618,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4596,33 +4628,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4635,60 +4671,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4702,7 +4742,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4712,33 +4752,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4795,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4761,7 +4805,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4771,40 +4815,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq40，推进3站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4812,29 +4860,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>物理seq24（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>08:12</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4844,33 +4876,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4883,60 +4919,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4950,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4960,33 +5000,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4999,60 +5043,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5066,7 +5114,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5076,33 +5124,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5167,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5125,7 +5177,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5135,40 +5187,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5182,7 +5238,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5192,33 +5248,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5291,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5241,7 +5301,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5251,40 +5311,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5298,7 +5362,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5308,33 +5372,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5415,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5357,7 +5425,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5367,40 +5435,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5414,7 +5486,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5424,33 +5496,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5463,32 +5539,32 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq62，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5511,12 +5587,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5524,13 +5600,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr"/>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5566,7 +5658,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5579,60 +5671,64 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5646,7 +5742,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5656,17 +5752,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5676,13 +5772,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5695,60 +5795,64 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5762,7 +5866,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5772,33 +5876,37 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5919,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5821,7 +5929,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5831,12 +5939,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq54，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5859,12 +5967,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5872,13 +5980,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr"/>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5914,7 +6034,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5927,7 +6047,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5937,7 +6057,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5975,12 +6095,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5994,7 +6114,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6030,7 +6150,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6163,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6053,7 +6173,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6091,12 +6211,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6110,7 +6230,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6146,7 +6266,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6279,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6169,7 +6289,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6207,12 +6327,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6226,7 +6346,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6262,7 +6382,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6395,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6285,7 +6405,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6323,12 +6443,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6342,7 +6462,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6378,7 +6498,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6391,22 +6511,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6439,12 +6559,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6458,7 +6578,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6494,7 +6614,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6507,22 +6627,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6555,12 +6675,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6574,7 +6694,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6610,7 +6730,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6623,22 +6743,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6671,12 +6791,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6690,7 +6810,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6715,22 +6835,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6743,22 +6859,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6796,7 +6912,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6810,7 +6926,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6835,22 +6951,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6863,22 +6975,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6911,12 +7023,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6930,7 +7042,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6966,7 +7078,7 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6979,7 +7091,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6989,7 +7101,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7027,12 +7139,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7046,7 +7158,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7071,22 +7183,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7099,22 +7207,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7152,7 +7260,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7166,7 +7274,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7191,92 +7299,84 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7290,7 +7390,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7300,107 +7400,99 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7414,7 +7506,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7424,17 +7516,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7449,82 +7541,78 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7538,7 +7626,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7548,17 +7636,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7573,82 +7661,78 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7662,7 +7746,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7672,107 +7756,99 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7786,7 +7862,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7796,17 +7872,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7821,82 +7897,78 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7910,7 +7982,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7920,17 +7992,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7945,40 +8017,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -8011,12 +8083,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8030,7 +8102,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8055,46 +8127,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8127,12 +8203,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8146,7 +8222,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8181,40 +8257,40 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8247,12 +8323,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8266,7 +8342,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8291,46 +8367,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8363,12 +8443,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8382,7 +8462,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8407,46 +8487,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8479,12 +8563,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8498,7 +8582,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8523,50 +8607,46 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8599,12 +8679,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8618,7 +8698,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8653,40 +8733,40 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8719,12 +8799,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8738,7 +8818,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8763,46 +8843,50 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8835,12 +8919,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8854,7 +8938,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8889,12 +8973,12 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8907,52 +8991,56 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8960,7 +9048,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8974,7 +9062,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8984,37 +9072,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9027,60 +9115,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9094,7 +9186,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9104,33 +9196,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9239,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9153,7 +9249,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9163,32 +9259,36 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9196,7 +9296,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9210,7 +9310,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9220,37 +9320,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9363,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9273,7 +9373,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9283,40 +9383,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9330,43 +9434,2695 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC74" s="2" t="inlineStr"/>
-      <c r="AD74" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-operations.xlsx
+++ b/data/export/2026-10-04-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5804,17 +5804,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6796,17 +6796,17 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7912,17 +7912,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9276,17 +9276,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9825,24 +9825,24 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9939,32 +9939,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9972,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9996,17 +10000,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10016,17 +10020,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -10059,32 +10063,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10092,7 +10100,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10116,17 +10124,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10136,17 +10144,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10332,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10386,7 +10394,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10460,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10496,17 +10504,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10638,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10832,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -11002,7 +11010,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11498,7 +11506,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11576,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11692,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11736,17 +11744,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12014,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12084,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12120,17 +12128,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12204,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12262,7 +12270,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12340,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12386,7 +12394,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12518,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12638,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12708,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12948,7 +12956,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13002,7 +13010,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13204,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13245,12 +13253,12 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13452,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13568,7 +13576,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13612,17 +13620,17 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13754,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13874,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14060,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14176,7 +14184,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14478,7 +14486,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14734,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14804,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -15044,7 +15052,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15088,17 +15096,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15176,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15288,7 +15296,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15332,17 +15340,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -15466,7 +15474,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15598,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -15660,7 +15668,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15714,7 +15722,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15792,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15962,7 +15970,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16040,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16086,7 +16094,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16342,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -16458,7 +16466,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16536,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16776,7 +16784,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16954,7 +16962,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17218,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -17454,7 +17462,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17532,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17578,7 +17586,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -17702,7 +17710,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -17826,7 +17834,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18028,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18074,7 +18082,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -18198,7 +18206,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -18322,7 +18330,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18702,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -19144,7 +19152,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19188,17 +19196,17 @@
       </c>
       <c r="AB151" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -19268,7 +19276,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19317,12 +19325,12 @@
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19400,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19436,17 +19444,17 @@
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19524,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19560,17 +19568,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -19640,7 +19648,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19694,7 +19702,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -19764,7 +19772,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19888,7 +19896,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -20008,7 +20016,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20132,7 +20140,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20256,7 +20264,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20380,7 +20388,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20504,7 +20512,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20558,7 +20566,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -20682,7 +20690,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -20806,7 +20814,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -21054,7 +21062,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21562,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -21711,32 +21719,36 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N172" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -21744,7 +21756,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21768,17 +21780,17 @@
       </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA172" s="2" t="inlineStr">
@@ -21788,17 +21800,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -21841,24 +21853,24 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
@@ -21868,7 +21880,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21917,12 +21929,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -21960,7 +21972,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -21988,7 +22000,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22091,32 +22103,36 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22124,7 +22140,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22148,17 +22164,17 @@
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA175" s="2" t="inlineStr">
@@ -22168,17 +22184,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -22211,32 +22227,36 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N176" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22244,7 +22264,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22268,17 +22288,17 @@
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA176" s="2" t="inlineStr">
@@ -22288,17 +22308,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -22364,7 +22384,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22418,7 +22438,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22471,12 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq41，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22484,7 +22504,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22492,10 +22512,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R178" s="2" t="inlineStr"/>
-      <c r="S178" s="2" t="inlineStr"/>
-      <c r="T178" s="2" t="inlineStr"/>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置迎春路金松路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -22604,7 +22640,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22724,7 +22760,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22844,7 +22880,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22898,7 +22934,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -22964,7 +23000,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23084,7 +23120,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23204,7 +23240,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23258,7 +23294,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -23948,7 +23984,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23997,7 +24033,7 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
@@ -24126,7 +24162,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -24320,7 +24356,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24369,12 +24405,12 @@
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -24444,7 +24480,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24493,7 +24529,7 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
@@ -24816,7 +24852,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24860,12 +24896,12 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
@@ -25312,7 +25348,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25361,7 +25397,7 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
@@ -25436,7 +25472,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25560,7 +25596,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25604,12 +25640,12 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -25684,7 +25720,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25728,17 +25764,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -25862,7 +25898,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -26056,7 +26092,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26105,12 +26141,12 @@
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -26304,7 +26340,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26353,7 +26389,7 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26796,7 +26832,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26840,12 +26876,12 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
@@ -26920,7 +26956,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26969,7 +27005,7 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
@@ -27044,7 +27080,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27088,17 +27124,17 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -27168,7 +27204,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27416,7 +27452,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27460,12 +27496,12 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
@@ -27540,7 +27576,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27589,7 +27625,7 @@
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
@@ -27718,7 +27754,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -27912,7 +27948,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27956,12 +27992,12 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
@@ -28160,7 +28196,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28408,7 +28444,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28452,12 +28488,12 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
@@ -28532,7 +28568,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28576,17 +28612,17 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -28710,7 +28746,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -28780,7 +28816,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28824,17 +28860,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -29400,7 +29436,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29444,17 +29480,17 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -29524,7 +29560,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29573,12 +29609,12 @@
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -29648,7 +29684,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29692,17 +29728,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -29772,7 +29808,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29821,7 +29857,7 @@
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
@@ -29950,7 +29986,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -30268,7 +30304,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30312,12 +30348,12 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
@@ -30516,7 +30552,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30640,7 +30676,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30689,12 +30725,12 @@
       </c>
       <c r="AC244" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30888,7 +30924,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30937,7 +30973,7 @@
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
@@ -31012,7 +31048,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31061,7 +31097,7 @@
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
@@ -31136,7 +31172,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31180,17 +31216,17 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -31260,7 +31296,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31304,12 +31340,12 @@
       </c>
       <c r="AB249" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
@@ -31438,7 +31474,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -31508,7 +31544,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31552,17 +31588,17 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -32004,7 +32040,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32048,12 +32084,12 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
@@ -32252,7 +32288,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32620,7 +32656,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32669,7 +32705,7 @@
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -32744,7 +32780,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32793,12 +32829,12 @@
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -32864,7 +32900,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32908,17 +32944,17 @@
       </c>
       <c r="AB262" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -32984,7 +33020,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33028,12 +33064,12 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33108,7 +33144,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33157,7 +33193,7 @@
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
@@ -33232,7 +33268,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33276,17 +33312,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -33534,7 +33570,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -33844,7 +33880,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33888,12 +33924,12 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
@@ -34092,7 +34128,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34437,24 +34473,24 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr"/>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N275" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O275" s="2" t="inlineStr">
@@ -34464,7 +34500,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34513,7 +34549,7 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34561,24 +34597,24 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr"/>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O276" s="2" t="inlineStr">
@@ -34588,7 +34624,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34637,12 +34673,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -34675,32 +34711,36 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N277" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O277" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34708,7 +34748,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34732,17 +34772,17 @@
       </c>
       <c r="X277" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z277" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA277" s="2" t="inlineStr">
@@ -34752,17 +34792,17 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -35045,24 +35085,24 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr"/>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N280" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O280" s="2" t="inlineStr">
@@ -35072,7 +35112,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35121,7 +35161,7 @@
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
@@ -35159,32 +35199,36 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N281" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35192,7 +35236,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35216,17 +35260,17 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA281" s="2" t="inlineStr">
@@ -35236,12 +35280,12 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35279,32 +35323,36 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr"/>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N282" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O282" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -35312,7 +35360,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35336,17 +35384,17 @@
       </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA282" s="2" t="inlineStr">
@@ -35356,17 +35404,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35399,32 +35447,36 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N283" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O283" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35432,7 +35484,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35456,17 +35508,17 @@
       </c>
       <c r="X283" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA283" s="2" t="inlineStr">
@@ -35476,12 +35528,12 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
@@ -35552,7 +35604,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35672,7 +35724,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35716,12 +35768,12 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35792,7 +35844,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35836,17 +35888,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-operations.xlsx
+++ b/data/export/2026-10-04-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7292,17 +7292,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8284,17 +8284,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9524,17 +9524,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10073,24 +10073,24 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10149,12 +10149,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -10187,32 +10187,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10220,7 +10224,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10244,17 +10248,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10264,17 +10268,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10460,7 +10464,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10832,7 +10836,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -11328,7 +11332,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11576,7 +11580,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -12084,7 +12088,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12340,7 +12344,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12708,7 +12712,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12752,12 +12756,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
@@ -12956,7 +12960,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13452,7 +13456,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13576,7 +13580,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -14060,7 +14064,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14184,7 +14188,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14804,7 +14808,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -15176,7 +15180,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15296,7 +15300,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15668,7 +15672,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15792,7 +15796,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15836,12 +15840,12 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
@@ -16040,7 +16044,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16536,7 +16540,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16784,7 +16788,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -18028,7 +18032,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -19400,7 +19404,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19524,7 +19528,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19772,7 +19776,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19816,12 +19820,12 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19896,7 +19900,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -20016,7 +20020,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20140,7 +20144,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20264,7 +20268,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20388,7 +20392,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20512,7 +20516,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -21972,7 +21976,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -22000,7 +22004,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22140,7 +22144,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22249,12 +22253,12 @@
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O176" s="2" t="inlineStr">
@@ -22264,7 +22268,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22476,7 +22480,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq41，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq52，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22504,7 +22508,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22607,32 +22611,36 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N179" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22640,7 +22648,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22664,17 +22672,17 @@
       </c>
       <c r="X179" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA179" s="2" t="inlineStr">
@@ -22684,12 +22692,12 @@
       </c>
       <c r="AB179" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
@@ -22760,7 +22768,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22880,7 +22888,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -23000,7 +23008,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23120,7 +23128,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23240,7 +23248,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -24534,7 +24542,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24860,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24901,12 +24909,12 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -25472,7 +25480,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25516,12 +25524,12 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
@@ -25596,7 +25604,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -26394,7 +26402,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -26832,7 +26840,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26881,12 +26889,12 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -27204,7 +27212,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27248,12 +27256,12 @@
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27452,7 +27460,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27630,7 +27638,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -27948,7 +27956,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27997,12 +28005,12 @@
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28204,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28240,12 +28248,12 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28444,7 +28452,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28816,7 +28824,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -29684,7 +29692,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29862,7 +29870,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -30304,7 +30312,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30353,12 +30361,12 @@
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -30552,7 +30560,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30596,12 +30604,12 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
@@ -31102,7 +31110,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -31296,7 +31304,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31544,7 +31552,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -32040,7 +32048,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32089,12 +32097,12 @@
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -32288,7 +32296,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32332,12 +32340,12 @@
       </c>
       <c r="AB257" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
@@ -33020,7 +33028,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33198,7 +33206,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -33268,7 +33276,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33880,7 +33888,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33929,12 +33937,12 @@
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -34128,7 +34136,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34172,12 +34180,12 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -35166,7 +35174,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -35236,7 +35244,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35360,7 +35368,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35457,24 +35465,24 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O283" s="2" t="inlineStr">
@@ -35484,7 +35492,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35533,12 +35541,12 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -35571,32 +35579,36 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N284" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O284" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35604,7 +35616,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35628,17 +35640,17 @@
       </c>
       <c r="X284" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA284" s="2" t="inlineStr">
@@ -35648,12 +35660,12 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35724,7 +35736,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35844,7 +35856,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">

--- a/data/export/2026-10-04-operations.xlsx
+++ b/data/export/2026-10-04-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3944,17 +3944,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5804,17 +5804,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7416,17 +7416,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7912,17 +7912,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8532,17 +8532,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9976,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10020,17 +10020,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10273,12 +10273,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -10311,32 +10311,36 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10344,7 +10348,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10368,17 +10372,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10388,17 +10392,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -10431,32 +10435,36 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10464,7 +10472,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10488,17 +10496,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10508,17 +10516,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10650,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10844,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10880,17 +10888,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11022,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11146,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11270,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11340,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11376,17 +11384,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11518,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11588,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11624,17 +11632,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11766,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12026,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12150,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12282,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -12344,7 +12352,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12522,7 +12530,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12650,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12720,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12960,7 +12968,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13004,17 +13012,17 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13146,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -13262,7 +13270,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13518,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13766,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13886,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14072,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14118,7 +14126,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14196,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14232,17 +14240,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14374,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14498,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14622,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14746,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14816,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14852,17 +14860,17 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -15110,7 +15118,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -15180,7 +15188,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15224,17 +15232,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15362,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15486,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15610,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15680,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15796,7 +15804,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15974,7 +15982,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16052,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16088,17 +16096,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16230,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16354,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -16470,7 +16478,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -16594,7 +16602,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16726,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16796,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16842,7 +16850,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -16966,7 +16974,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -17222,7 +17230,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17474,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17598,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -17714,7 +17722,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -17838,7 +17846,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17970,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18040,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18076,17 +18084,17 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -18210,7 +18218,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -18334,7 +18342,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -18458,7 +18466,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -18706,7 +18714,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -18830,7 +18838,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -19210,7 +19218,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19342,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -19582,7 +19590,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19714,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19784,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19900,7 +19908,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19944,17 +19952,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20082,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -20144,7 +20152,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20188,17 +20196,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20276,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20322,7 +20330,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -20392,7 +20400,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20436,17 +20444,17 @@
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20524,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20694,7 +20702,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -20818,7 +20826,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -21066,7 +21074,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21198,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -21566,7 +21574,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -21690,7 +21698,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -21814,7 +21822,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -21938,7 +21946,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -22074,7 +22082,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -22198,7 +22206,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22450,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22488,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq52，推进19站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq62，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22508,7 +22516,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22578,7 +22586,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22656,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22735,32 +22743,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22768,7 +22780,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22792,17 +22804,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22812,17 +22824,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -22855,32 +22867,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -22888,7 +22904,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22912,17 +22928,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22932,17 +22948,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -22975,32 +22991,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -23008,7 +23028,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23032,17 +23052,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -23052,17 +23072,17 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -23095,32 +23115,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -23128,7 +23152,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23152,17 +23176,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23172,17 +23196,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -23248,7 +23272,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23550,7 +23574,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -23922,7 +23946,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24814,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -25162,7 +25186,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -25286,7 +25310,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -25480,7 +25504,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25529,7 +25553,7 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
@@ -25604,7 +25628,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25648,17 +25672,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26278,7 +26302,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -26770,7 +26794,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -27212,7 +27236,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27261,7 +27285,7 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27460,7 +27484,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27504,17 +27528,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28158,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28204,7 +28228,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28253,7 +28277,7 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28382,7 +28406,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -28452,7 +28476,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28496,17 +28520,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -28824,7 +28848,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -29002,7 +29026,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -29126,7 +29150,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -29250,7 +29274,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -29692,7 +29716,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -30118,7 +30142,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -30242,7 +30266,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30560,7 +30584,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30609,7 +30633,7 @@
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
@@ -30862,7 +30886,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -31304,7 +31328,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31348,17 +31372,17 @@
       </c>
       <c r="AB249" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31552,7 +31576,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31854,7 +31878,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -32226,7 +32250,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -32296,7 +32320,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32345,7 +32369,7 @@
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
@@ -32474,7 +32498,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -33028,7 +33052,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33072,17 +33096,17 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33300,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33818,7 +33842,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34066,7 +34090,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -34136,7 +34160,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34185,7 +34209,7 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -34438,7 +34462,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -35244,7 +35268,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35288,17 +35312,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -35368,7 +35392,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35589,24 +35613,24 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O284" s="2" t="inlineStr">
@@ -35616,7 +35640,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35665,7 +35689,7 @@
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35703,32 +35727,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35736,7 +35764,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35760,17 +35788,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35780,17 +35808,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -35856,7 +35884,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
